--- a/public/imports/492_muangphet_Logistics.xlsx
+++ b/public/imports/492_muangphet_Logistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebApp\TSMC\tsmc_web\public\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D84AA0C-CCF9-4206-8136-05ED2CC2B684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A197BE6D-CC42-44D5-9B97-BE199270FE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,7 +741,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>25292</v>
+        <v>244438</v>
       </c>
       <c r="C3" s="6">
         <v>71</v>
@@ -821,7 +821,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>25290</v>
+        <v>244436</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>38</v>
@@ -901,7 +901,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>25288</v>
+        <v>244434</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>49</v>
@@ -981,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4">
-        <v>25286</v>
+        <v>244432</v>
       </c>
       <c r="C6" s="6">
         <v>71</v>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4">
-        <v>25284</v>
+        <v>244430</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>38</v>
@@ -1141,7 +1141,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>25282</v>
+        <v>244428</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>49</v>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>25280</v>
+        <v>244426</v>
       </c>
       <c r="C9" s="6">
         <v>71</v>
@@ -1301,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4">
-        <v>25278</v>
+        <v>244424</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>38</v>
@@ -1381,7 +1381,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>25276</v>
+        <v>244422</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>49</v>
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="4">
-        <v>25274</v>
+        <v>244420</v>
       </c>
       <c r="C12" s="6">
         <v>71</v>
@@ -1541,7 +1541,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4">
-        <v>25272</v>
+        <v>244418</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>38</v>
@@ -1621,7 +1621,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="4">
-        <v>25270</v>
+        <v>244416</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>49</v>
@@ -1701,7 +1701,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="4">
-        <v>25268</v>
+        <v>244414</v>
       </c>
       <c r="C15" s="6">
         <v>71</v>
@@ -1781,7 +1781,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="4">
-        <v>25266</v>
+        <v>244412</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>38</v>
@@ -1861,7 +1861,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="4">
-        <v>25264</v>
+        <v>244410</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>49</v>
@@ -1941,7 +1941,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="4">
-        <v>25261</v>
+        <v>244407</v>
       </c>
       <c r="C18" s="6">
         <v>71</v>
@@ -2021,7 +2021,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="4">
-        <v>25259</v>
+        <v>244405</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>38</v>
@@ -2101,7 +2101,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="4">
-        <v>25257</v>
+        <v>244403</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>49</v>
@@ -2181,7 +2181,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="4">
-        <v>25255</v>
+        <v>244401</v>
       </c>
       <c r="C21" s="6">
         <v>71</v>
@@ -2261,7 +2261,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="4">
-        <v>25253</v>
+        <v>244399</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>38</v>
@@ -2341,7 +2341,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="4">
-        <v>25251</v>
+        <v>244397</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>49</v>
@@ -2421,7 +2421,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="4">
-        <v>25249</v>
+        <v>244395</v>
       </c>
       <c r="C24" s="6">
         <v>71</v>
@@ -2501,7 +2501,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="4">
-        <v>25247</v>
+        <v>244393</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>38</v>
@@ -2581,7 +2581,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="4">
-        <v>25245</v>
+        <v>244391</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>49</v>
@@ -2661,7 +2661,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="4">
-        <v>25243</v>
+        <v>244389</v>
       </c>
       <c r="C27" s="6">
         <v>71</v>
@@ -2741,7 +2741,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="4">
-        <v>25241</v>
+        <v>244387</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>38</v>
@@ -2821,7 +2821,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="4">
-        <v>25239</v>
+        <v>244385</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>49</v>
@@ -2901,7 +2901,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="4">
-        <v>25237</v>
+        <v>244383</v>
       </c>
       <c r="C30" s="6">
         <v>71</v>
@@ -2981,7 +2981,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="4">
-        <v>25235</v>
+        <v>244381</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>38</v>
@@ -3061,7 +3061,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="4">
-        <v>25233</v>
+        <v>244379</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>49</v>
@@ -3141,7 +3141,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="4">
-        <v>25231</v>
+        <v>244377</v>
       </c>
       <c r="C33" s="6">
         <v>71</v>
@@ -3221,7 +3221,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="4">
-        <v>25229</v>
+        <v>244375</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>38</v>
@@ -3301,7 +3301,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="4">
-        <v>25227</v>
+        <v>244373</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>49</v>
@@ -3381,7 +3381,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="4">
-        <v>25225</v>
+        <v>244371</v>
       </c>
       <c r="C36" s="6">
         <v>71</v>
@@ -3461,7 +3461,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="4">
-        <v>25223</v>
+        <v>244369</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>38</v>
@@ -3541,7 +3541,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="4">
-        <v>25221</v>
+        <v>244367</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>49</v>
@@ -3621,7 +3621,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="4">
-        <v>25219</v>
+        <v>244365</v>
       </c>
       <c r="C39" s="6">
         <v>71</v>
@@ -3701,7 +3701,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="4">
-        <v>25217</v>
+        <v>244363</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>38</v>
@@ -3781,7 +3781,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="4">
-        <v>25215</v>
+        <v>244361</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>49</v>
@@ -3861,7 +3861,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="4">
-        <v>25213</v>
+        <v>244359</v>
       </c>
       <c r="C42" s="6">
         <v>71</v>
@@ -3941,7 +3941,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4">
-        <v>25211</v>
+        <v>244357</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>38</v>
@@ -4021,7 +4021,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="4">
-        <v>25209</v>
+        <v>244355</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>49</v>
@@ -4101,7 +4101,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="4">
-        <v>25207</v>
+        <v>244353</v>
       </c>
       <c r="C45" s="6">
         <v>71</v>
@@ -4181,7 +4181,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="4">
-        <v>25205</v>
+        <v>244351</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>38</v>
@@ -4261,7 +4261,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="4">
-        <v>25201</v>
+        <v>244347</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>49</v>
@@ -4341,7 +4341,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="4">
-        <v>25199</v>
+        <v>244345</v>
       </c>
       <c r="C48" s="6">
         <v>71</v>
@@ -4421,7 +4421,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="4">
-        <v>25197</v>
+        <v>244343</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>38</v>
@@ -4501,7 +4501,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="4">
-        <v>25195</v>
+        <v>244341</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>49</v>
@@ -4581,7 +4581,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="4">
-        <v>25193</v>
+        <v>244339</v>
       </c>
       <c r="C51" s="6">
         <v>71</v>
@@ -4661,7 +4661,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="4">
-        <v>25191</v>
+        <v>244337</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>38</v>
@@ -4741,7 +4741,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="4">
-        <v>25189</v>
+        <v>244335</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>49</v>
@@ -4821,7 +4821,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="4">
-        <v>25187</v>
+        <v>244333</v>
       </c>
       <c r="C54" s="6">
         <v>71</v>
@@ -4901,7 +4901,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="4">
-        <v>25185</v>
+        <v>244331</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>38</v>
@@ -4981,7 +4981,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="4">
-        <v>25183</v>
+        <v>244329</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>49</v>
@@ -5061,7 +5061,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="4">
-        <v>25181</v>
+        <v>244327</v>
       </c>
       <c r="C57" s="6">
         <v>71</v>
@@ -5141,7 +5141,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="4">
-        <v>25179</v>
+        <v>244325</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>38</v>
@@ -5221,7 +5221,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="4">
-        <v>25177</v>
+        <v>244323</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>49</v>
@@ -5301,7 +5301,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="4">
-        <v>25175</v>
+        <v>244321</v>
       </c>
       <c r="C60" s="6">
         <v>71</v>
@@ -5381,7 +5381,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="4">
-        <v>25173</v>
+        <v>244319</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>38</v>
@@ -5461,7 +5461,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="4">
-        <v>25172</v>
+        <v>244318</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>49</v>
@@ -5541,7 +5541,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="4">
-        <v>25170</v>
+        <v>244316</v>
       </c>
       <c r="C63" s="6">
         <v>71</v>
@@ -5621,7 +5621,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="4">
-        <v>25168</v>
+        <v>244314</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>38</v>
@@ -5701,7 +5701,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="4">
-        <v>25166</v>
+        <v>244312</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>49</v>
@@ -5781,7 +5781,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4">
-        <v>25164</v>
+        <v>244310</v>
       </c>
       <c r="C66" s="6">
         <v>71</v>
@@ -5861,7 +5861,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="4">
-        <v>25162</v>
+        <v>244308</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>38</v>
@@ -5941,7 +5941,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="4">
-        <v>25160</v>
+        <v>244306</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>49</v>
@@ -6021,7 +6021,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="4">
-        <v>25158</v>
+        <v>244304</v>
       </c>
       <c r="C69" s="6">
         <v>71</v>
@@ -6101,7 +6101,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="4">
-        <v>25156</v>
+        <v>244302</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>38</v>
@@ -6181,7 +6181,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="4">
-        <v>25154</v>
+        <v>244300</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>49</v>
@@ -6261,7 +6261,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="4">
-        <v>25152</v>
+        <v>244298</v>
       </c>
       <c r="C72" s="6">
         <v>71</v>
@@ -6341,7 +6341,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="4">
-        <v>25150</v>
+        <v>244296</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>38</v>
@@ -6421,7 +6421,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="4">
-        <v>25148</v>
+        <v>244294</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>49</v>
@@ -6501,7 +6501,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="4">
-        <v>25146</v>
+        <v>244292</v>
       </c>
       <c r="C75" s="6">
         <v>71</v>
@@ -6581,7 +6581,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="4">
-        <v>25144</v>
+        <v>244290</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>38</v>
@@ -6661,7 +6661,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="4">
-        <v>25140</v>
+        <v>244286</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>49</v>
@@ -6741,7 +6741,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="4">
-        <v>25138</v>
+        <v>244284</v>
       </c>
       <c r="C78" s="6">
         <v>71</v>
@@ -6821,7 +6821,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="4">
-        <v>25136</v>
+        <v>244282</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>38</v>
@@ -6901,7 +6901,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="4">
-        <v>25134</v>
+        <v>244280</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>49</v>
@@ -6981,7 +6981,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="4">
-        <v>25132</v>
+        <v>244278</v>
       </c>
       <c r="C81" s="6">
         <v>71</v>
@@ -7061,7 +7061,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="4">
-        <v>25130</v>
+        <v>244276</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>38</v>
@@ -7141,7 +7141,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="4">
-        <v>25128</v>
+        <v>244274</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>49</v>
@@ -7221,7 +7221,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="4">
-        <v>25126</v>
+        <v>244272</v>
       </c>
       <c r="C84" s="6">
         <v>71</v>
@@ -7301,7 +7301,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="4">
-        <v>25124</v>
+        <v>244270</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>38</v>
@@ -7381,7 +7381,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="4">
-        <v>25122</v>
+        <v>244268</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>49</v>
@@ -7461,7 +7461,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="4">
-        <v>25120</v>
+        <v>244266</v>
       </c>
       <c r="C87" s="6">
         <v>71</v>
@@ -7541,7 +7541,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="4">
-        <v>25118</v>
+        <v>244264</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>38</v>
@@ -7621,7 +7621,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="4">
-        <v>25116</v>
+        <v>244262</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>49</v>
@@ -7701,7 +7701,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="4">
-        <v>25114</v>
+        <v>244260</v>
       </c>
       <c r="C90" s="6">
         <v>71</v>
@@ -7781,7 +7781,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="4">
-        <v>25112</v>
+        <v>244258</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>38</v>
@@ -7865,6 +7865,19 @@
     <filterColumn colId="21" showButton="0"/>
   </autoFilter>
   <mergeCells count="21">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="Z1:Z2"/>
@@ -7873,19 +7886,6 @@
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="R1:W1"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
